--- a/human_validation/judge/kor/judge_D007_S003_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D007_S003_P002__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,229 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 시작하기 전에, 오늘 어떤 일로 오시게 되었는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 먹는 게 진짜 엉망이 됐어요. 근무 전날엔 커피랑 그래놀라바 하나 겨우 먹는 게 다인 날도 있고요. 요즘 수술복이 헐렁하게 걸치는데, 일부러 살 빼려고 한 것도 아니거든요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이렇게 적게 드시는 게, 일부러 체중이 느는 걸 피하려고 하시거나 체형에 대해 걱정이 있어서인가요, 아니면 그냥 입맛이 없거나 먹을 시간이 없는 느낌에 더 가까운가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 아니요, 살을 빼려거나 찌는 걸 피하려는 건 아니에요. 그냥... 딱히 많이 안 먹게 되는 것 같아요. 출근 전에 커피랑 그래놀라바 하나 정도 먹고 나면 그대로 하루가 시작돼요. 요즘 수술복이 헐렁한데, 일부러 그런 게 아니라서 좀 걱정돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 지난 몇 주 동안 눈에 띄게 기분이 가라앉거나 슬프셨거나, 평소에 즐기시던 일들에 흥미나 즐거움이 별로 없으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네. 거의 매일 아침 뭔가 무겁고 텅 빈 느낌으로 눈을 떠요. 사원증도 달기 전에 하루가 이미 망한 것 같은 느낌이랄까요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 몸을 움직이지 않는데도 심장이 빨리 뛰거나, 평소와 달리 덥거나 땀이 나거나, 손이 떨리는 것 같은 신체 증상을 느끼신 적 있으세요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 그런 건 딱히 못 느꼈어요. 네, 생각나는 게 없네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 이 무겁고 텅 빈 느낌과 흥미 상실이 지난 2주 이상 거의 매일 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네. 적어도 지난 2주 동안은 거의 매일 아침 그랬어요. 무겁고 텅 빈 느낌으로 일어나는데, 출근도 하기 전에 하루가 이미 망한 것 같은 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 아침에 무겁고 텅 빈 느낌 말고도, 취미나 친구들과 보내는 시간처럼 예전에 좋아하시던 일들에 흥미나 즐거움이 줄어든 걸 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네. 예전엔 밴 코틀랜드 공원에서 달리기도 하고, 사진도 찍고, 친구들이랑 체스도 뒀거든요. 근데 요즘은 그냥 '이게 무슨 의미가 있나' 싶은 생각만 들고, 집에서 폰만 보거나 예산 스프레드시트나 확인하게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 특별히 활동을 많이 하지 않으셨는데도 거의 매일 평소보다 유난히 피곤하거나 기운이 없으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 네. 밤에 푹 자고 나서도 마치 더블 교대를 뛴 것처럼 느껴져요. 점심때쯤 되면 생각을 제대로 붙잡고 있는 것도 힘들 정도예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 스스로를 다치게 하고 싶다는 생각이나, 차라리 여기 없는 게 낫겠다는 생각을 하신 적 있으세요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 자해할 계획을 세운 적은 없어요. 근데... 네, 가끔 그냥 안 깨어났으면 좋겠다는 생각이 들 때가 있어요. 아니면 그냥 사라지면 좀 더 편할 것 같다는 생각도 들고요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 주요우울장애 (D013); 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 며칠 이상 유난히 활기차거나 들뜨고, 평소보다 잠을 훨씬 적게 자도 괜찮았던 시기, 그리고 생각이 빠르게 흘러가거나 평소보다 자신감이 넘쳤던 시기가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 잘 모르겠어요. 특별히 활기가 넘치거나 잠을 훨씬 적게 자도 됐던 시기는 딱히 없었던 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 주요우울장애 (D013); 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 범불안장애 (D011); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 이런 증상들이 직장에서의 업무 수행이나 일상적인 책임을 다하는 데 영향을 미치고 있나요? 예를 들어 근무를 빠지거나, 업무에 집중하는 게 힘들거나, 하루를 버티는 데 다른 사람의 도움이 필요하다거나 하는 식으로요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 네. 평소라면 안 했을 실수들을 직장에서 하고 있고, 가끔은 아주 간단한 요청도 동료들이 다시 말해줘야 할 때가 있어요. 체스 모임이랑 사진 산책도 안 가게 됐어요. 제가 잘 따라갈 수 있을지, 사람들 앞에서 평소처럼 행동할 수 있을지 스스로 믿음이 안 가서요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 주요우울장애 (D013); 지속성 우울장애 (D014) | 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>진단명: 조현정동장애 (우울형) (D007)
 인구통계: 성별 남성 / 나이 46 / 직업상태 healthcare support worker / 최종학력 전문학사
@@ -575,296 +789,49 @@
 증상 지속 기간: 1 year and 11 months
 추가 요건: psychotic_symptoms and depressive_episode occur concurrently, depressive_episode is present for the majority of the total duration of the active and residual portions of the illness (Criterion C), delusions_and_hallucinations occur for 2 or more weeks in the absence of a major mood episode (Criterion B)
 주호소 증상 코드: S026
-배경 서술: 제임스가 근무하던 병원이 전자의무기록(EMR) 시스템과 업무 절차를 전면 개편하면서 인력 배치를 재조정했고, 그는 예측 가능했던 환자 지원 업무 일정에서 벗어나 접수, 채혈, 교육까지 추가된 교대 근무제로 옮겨가게 되었다. 이후 1년 11개월에 걸쳐 이런 변화는 그가 마음의 중심을 잡기 위해 의지했던 일상들—밴 코틀랜드 공원에서의 달리기, 사진 산책, 체스 모임, 자격증 공부—을 무너뜨렸고, 그의 우울 증상 악화는 기분이 가장 저조할 때만이 아니라 지속적으로 나타나는 정신증적 경험과 함께 진행되었다. 동료들이 그의 의사소통을 따라가기 어려워할 정도로 업무 수행 능력이 저하되었고, 평범한 직장 내 상호작용에서의 자신감도 떨어졌지만, 그는 목록 작성과 데이터 기록, 엄격한 예산 관리로 이를 보완하려 애썼다. 결국 그는 죽음에 대한 생각, 업무상의 실질적인 실수들, 그리고 자신의 지각에 대한 신뢰 상실이 혼자서는 안전하게 관리할 수 없는 수준이 되었다는 것을 깨닫고 직원 지원 프로그램을 통해 도움을 요청했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 시작하기 전에, 오늘 어떤 일로 오시게 되었는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 먹는 게 진짜 엉망이 됐어요. 근무 전날엔 커피랑 그래놀라바 하나 겨우 먹는 게 다인 날도 있고요. 요즘 수술복이 헐렁하게 걸치는데, 일부러 살 빼려고 한 것도 아니거든요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이렇게 적게 드시는 게, 일부러 체중이 느는 걸 피하려고 하시거나 체형에 대해 걱정이 있어서인가요, 아니면 그냥 입맛이 없거나 먹을 시간이 없는 느낌에 더 가까운가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 아니요, 살을 빼려거나 찌는 걸 피하려는 건 아니에요. 그냥... 딱히 많이 안 먹게 되는 것 같아요. 출근 전에 커피랑 그래놀라바 하나 정도 먹고 나면 그대로 하루가 시작돼요. 요즘 수술복이 헐렁한데, 일부러 그런 게 아니라서 좀 걱정돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 지난 몇 주 동안 눈에 띄게 기분이 가라앉거나 슬프셨거나, 평소에 즐기시던 일들에 흥미나 즐거움이 별로 없으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네. 거의 매일 아침 뭔가 무겁고 텅 빈 느낌으로 눈을 떠요. 사원증도 달기 전에 하루가 이미 망한 것 같은 느낌이랄까요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 몸을 움직이지 않는데도 심장이 빨리 뛰거나, 평소와 달리 덥거나 땀이 나거나, 손이 떨리는 것 같은 신체 증상을 느끼신 적 있으세요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 그런 건 딱히 못 느꼈어요. 네, 생각나는 게 없네요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 이 무겁고 텅 빈 느낌과 흥미 상실이 지난 2주 이상 거의 매일 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네. 적어도 지난 2주 동안은 거의 매일 아침 그랬어요. 무겁고 텅 빈 느낌으로 일어나는데, 출근도 하기 전에 하루가 이미 망한 것 같은 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 아침에 무겁고 텅 빈 느낌 말고도, 취미나 친구들과 보내는 시간처럼 예전에 좋아하시던 일들에 흥미나 즐거움이 줄어든 걸 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네. 예전엔 밴 코틀랜드 공원에서 달리기도 하고, 사진도 찍고, 친구들이랑 체스도 뒀거든요. 근데 요즘은 그냥 '이게 무슨 의미가 있나' 싶은 생각만 들고, 집에서 폰만 보거나 예산 스프레드시트나 확인하게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 특별히 활동을 많이 하지 않으셨는데도 거의 매일 평소보다 유난히 피곤하거나 기운이 없으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 네. 밤에 푹 자고 나서도 마치 더블 교대를 뛴 것처럼 느껴져요. 점심때쯤 되면 생각을 제대로 붙잡고 있는 것도 힘들 정도예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 스스로를 다치게 하고 싶다는 생각이나, 차라리 여기 없는 게 낫겠다는 생각을 하신 적 있으세요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 자해할 계획을 세운 적은 없어요. 근데... 네, 가끔 그냥 안 깨어났으면 좋겠다는 생각이 들 때가 있어요. 아니면 그냥 사라지면 좀 더 편할 것 같다는 생각도 들고요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 주요우울장애 (D013); 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 며칠 이상 유난히 활기차거나 들뜨고, 평소보다 잠을 훨씬 적게 자도 괜찮았던 시기, 그리고 생각이 빠르게 흘러가거나 평소보다 자신감이 넘쳤던 시기가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 잘 모르겠어요. 특별히 활기가 넘치거나 잠을 훨씬 적게 자도 됐던 시기는 딱히 없었던 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 주요우울장애 (D013); 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 범불안장애 (D011); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 이런 증상들이 직장에서의 업무 수행이나 일상적인 책임을 다하는 데 영향을 미치고 있나요? 예를 들어 근무를 빠지거나, 업무에 집중하는 게 힘들거나, 하루를 버티는 데 다른 사람의 도움이 필요하다거나 하는 식으로요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 네. 평소라면 안 했을 실수들을 직장에서 하고 있고, 가끔은 아주 간단한 요청도 동료들이 다시 말해줘야 할 때가 있어요. 체스 모임이랑 사진 산책도 안 가게 됐어요. 제가 잘 따라갈 수 있을지, 사람들 앞에서 평소처럼 행동할 수 있을지 스스로 믿음이 안 가서요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
+배경 서술: 제임스가 근무하던 병원이 전자의무기록(EMR) 시스템과 업무 절차를 전면 개편하면서 인력 배치를 재조정했고, 그는 예측 가능했던 환자 지원 업무 일정에서 벗어나 접수, 채혈, 교육까지 추가된 교대 근무제로 옮겨가게 되었다. 이후 1년 11개월에 걸쳐 이런 변화는 그가 마음의 중심을 잡기 위해 의지했던 일상들—밴 코틀랜드 공원에서의 달리기, 사진 산책, 체스 모임, 자격증 공부—을 무너뜨렸고, 그의 우울 증상 악화는 기분이 가장 저조할 때만이 아니라 지속적으로 나타나는 정신증적 경험과 함께 진행되었다. 동료들이 그의 의사소통을 따라가기 어려워할 정도로 업무 수행 능력이 저하되었고, 평범한 직장 내 상호작용에서의 자신감도 떨어졌지만, 그는 목록 작성과 데이터 기록, 엄격한 예산 관리로 이를 보완하려 애썼다. 결국 그는 죽음에 대한 생각, 업무상의 실질적인 실수들, 그리고 자신의 지각에 대한 신뢰 상실이 혼자서는 안전하게 관리할 수 없는 수준이 되었다는 것을 깨닫고 직원 지원 프로그램을 통해 도움을 요청했다.
+표집된 증상 목록:
+  - S019 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - S020 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+  - S021 와해된 사고/언어: 논리적이고 일관된 흐름이 부족해 말이나 생각이 흩어지고 따라가기 어려운 증상.
+  - S024 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - S025 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - S026 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S028 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.
+  - S029 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - S030 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - S032 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
+        </is>
+      </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>[10번째 턴 · 의사의 감별진단] 고확률: 주요우울장애 (D013); 지속성 우울장애 (D014) | 중간확률: 주의력결핍 과잉행동장애 (복합형) (D001); 주의력결핍 과잉행동장애 (부주의 우세형) (D002); 조현정동장애 (우울형) (D007); 범불안장애 (D011); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 주의력결핍 과잉행동장애 (과잉행동-충동 우세형) (D003) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 신경성 식욕부진증 (D021); 신경성 폭식증 (D022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.; 와해된 사고/언어: 논리적이고 일관된 흐름이 부족해 말이나 생각이 흩어지고 따라가기 어려운 증상.; 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.; 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=5, 커버리지=1.0)
-  확인된 근거: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.
-  누락: 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.</t>
+          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32.2)
+지속 기간 요건: 없음
+기능적 손상 요건: 있음
+추가 요건: 없음
+체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)
+체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=5, 커버리지=1.0)
+확인된 근거:
+  - 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.
+체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A46:B46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D007_S003_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D007_S003_P002__claude-sonnet-5_kor.xlsx
@@ -775,6 +775,11 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -827,11 +832,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A46:B46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D007_S003_P002__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D007_S003_P002__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.1186</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.1214</v>
+        <v>0.2167</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.5208</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.3333</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
